--- a/dynamical_DE_nonfid/cmb/all.xlsx
+++ b/dynamical_DE_nonfid/cmb/all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>183263462.2172973</v>
+        <v>179726318.7752797</v>
       </c>
       <c r="C2" t="n">
-        <v>-690028363.7085135</v>
+        <v>-684279674.308524</v>
       </c>
       <c r="D2" t="n">
-        <v>136211157.3364885</v>
+        <v>133164111.0842395</v>
       </c>
       <c r="E2" t="n">
-        <v>-4758041.809165712</v>
+        <v>-5301485.871778147</v>
       </c>
       <c r="F2" t="n">
-        <v>-57464445.72364189</v>
+        <v>-56142956.60137209</v>
       </c>
       <c r="G2" t="n">
-        <v>-12356919.54103419</v>
+        <v>-11998943.14466756</v>
       </c>
       <c r="H2" t="n">
-        <v>-6552094.486712468</v>
+        <v>-6436718.703385314</v>
       </c>
       <c r="I2" t="n">
-        <v>44549067.81327646</v>
+        <v>43485110.55453386</v>
       </c>
       <c r="J2" t="n">
-        <v>2340521.296071955</v>
+        <v>2538006.34661707</v>
       </c>
       <c r="K2" t="n">
-        <v>338416.3572458662</v>
+        <v>393523.3372458589</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-690028363.7085136</v>
+        <v>-684279674.3085241</v>
       </c>
       <c r="C3" t="n">
-        <v>3029247377.408856</v>
+        <v>3010811373.398757</v>
       </c>
       <c r="D3" t="n">
-        <v>-457608018.1746358</v>
+        <v>-453274471.6905276</v>
       </c>
       <c r="E3" t="n">
-        <v>32252610.62350188</v>
+        <v>33068744.31396467</v>
       </c>
       <c r="F3" t="n">
-        <v>223039436.2764482</v>
+        <v>221180647.2978463</v>
       </c>
       <c r="G3" t="n">
-        <v>47229957.04432949</v>
+        <v>46782212.50549188</v>
       </c>
       <c r="H3" t="n">
-        <v>23242409.41245245</v>
+        <v>23017830.30519351</v>
       </c>
       <c r="I3" t="n">
-        <v>-171644950.7877054</v>
+        <v>-170146067.9621255</v>
       </c>
       <c r="J3" t="n">
-        <v>-9264715.732167479</v>
+        <v>-9319113.296975804</v>
       </c>
       <c r="K3" t="n">
-        <v>-1364850.91401348</v>
+        <v>-1386726.105998227</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136211157.3364885</v>
+        <v>133164111.0842395</v>
       </c>
       <c r="C4" t="n">
-        <v>-457608018.1746358</v>
+        <v>-453274471.6905276</v>
       </c>
       <c r="D4" t="n">
-        <v>112075129.7679162</v>
+        <v>109374543.1721104</v>
       </c>
       <c r="E4" t="n">
-        <v>-1915047.001719781</v>
+        <v>-2368001.637530286</v>
       </c>
       <c r="F4" t="n">
-        <v>-38131002.56042391</v>
+        <v>-37002889.86396396</v>
       </c>
       <c r="G4" t="n">
-        <v>-7835262.707962726</v>
+        <v>-7528183.426049238</v>
       </c>
       <c r="H4" t="n">
-        <v>-5457936.244053065</v>
+        <v>-5358456.88315504</v>
       </c>
       <c r="I4" t="n">
-        <v>29583431.2794694</v>
+        <v>28675190.49999867</v>
       </c>
       <c r="J4" t="n">
-        <v>3655445.366674128</v>
+        <v>3826962.990752989</v>
       </c>
       <c r="K4" t="n">
-        <v>748678.0524112384</v>
+        <v>796448.5669007425</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-4758041.809165712</v>
+        <v>-5301485.871778147</v>
       </c>
       <c r="C5" t="n">
-        <v>32252610.62350187</v>
+        <v>33068744.31396466</v>
       </c>
       <c r="D5" t="n">
-        <v>-1915047.001719783</v>
+        <v>-2368001.637530287</v>
       </c>
       <c r="E5" t="n">
-        <v>1048669.440032667</v>
+        <v>936731.4425528144</v>
       </c>
       <c r="F5" t="n">
-        <v>1680654.917546056</v>
+        <v>1900676.716547794</v>
       </c>
       <c r="G5" t="n">
-        <v>318169.9970535817</v>
+        <v>379534.2690776868</v>
       </c>
       <c r="H5" t="n">
-        <v>113521.7920791233</v>
+        <v>129968.5455609026</v>
       </c>
       <c r="I5" t="n">
-        <v>-1294412.205567126</v>
+        <v>-1470976.294074424</v>
       </c>
       <c r="J5" t="n">
-        <v>-142884.5957050023</v>
+        <v>-101440.3649065482</v>
       </c>
       <c r="K5" t="n">
-        <v>-28538.92300987191</v>
+        <v>-17230.28742155878</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-57464445.72364189</v>
+        <v>-56142956.60137209</v>
       </c>
       <c r="C6" t="n">
-        <v>223039436.2764482</v>
+        <v>221180647.2978463</v>
       </c>
       <c r="D6" t="n">
-        <v>-38131002.56042391</v>
+        <v>-37002889.86396396</v>
       </c>
       <c r="E6" t="n">
-        <v>1680654.917546056</v>
+        <v>1900676.716547794</v>
       </c>
       <c r="F6" t="n">
-        <v>22366783.89713379</v>
+        <v>21822591.95535067</v>
       </c>
       <c r="G6" t="n">
-        <v>5249880.518372671</v>
+        <v>5099104.950243197</v>
       </c>
       <c r="H6" t="n">
-        <v>1590899.741068214</v>
+        <v>1551995.646661993</v>
       </c>
       <c r="I6" t="n">
-        <v>-17307477.90959779</v>
+        <v>-16869633.1802332</v>
       </c>
       <c r="J6" t="n">
-        <v>1355248.186992848</v>
+        <v>1254380.192172263</v>
       </c>
       <c r="K6" t="n">
-        <v>433025.4856837429</v>
+        <v>405463.7557837246</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-12356919.54103419</v>
+        <v>-11998943.14466756</v>
       </c>
       <c r="C7" t="n">
-        <v>47229957.04432949</v>
+        <v>46782212.50549188</v>
       </c>
       <c r="D7" t="n">
-        <v>-7835262.707962726</v>
+        <v>-7528183.426049238</v>
       </c>
       <c r="E7" t="n">
-        <v>318169.9970535817</v>
+        <v>379534.2690776868</v>
       </c>
       <c r="F7" t="n">
-        <v>5249880.518372671</v>
+        <v>5099104.950243197</v>
       </c>
       <c r="G7" t="n">
-        <v>1281325.387135033</v>
+        <v>1239055.078393945</v>
       </c>
       <c r="H7" t="n">
-        <v>294916.8015481419</v>
+        <v>284765.0145282443</v>
       </c>
       <c r="I7" t="n">
-        <v>-4086739.665400695</v>
+        <v>-3965440.212841945</v>
       </c>
       <c r="J7" t="n">
-        <v>532405.5943472488</v>
+        <v>502416.114790782</v>
       </c>
       <c r="K7" t="n">
-        <v>155215.9934330436</v>
+        <v>147070.6367823817</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-6552094.486712468</v>
+        <v>-6436718.703385314</v>
       </c>
       <c r="C8" t="n">
-        <v>23242409.41245245</v>
+        <v>23017830.30519351</v>
       </c>
       <c r="D8" t="n">
-        <v>-5457936.244053065</v>
+        <v>-5358456.88315504</v>
       </c>
       <c r="E8" t="n">
-        <v>113521.7920791233</v>
+        <v>129968.5455609026</v>
       </c>
       <c r="F8" t="n">
-        <v>1590899.741068214</v>
+        <v>1551995.646661993</v>
       </c>
       <c r="G8" t="n">
-        <v>294916.8015481419</v>
+        <v>284765.0145282443</v>
       </c>
       <c r="H8" t="n">
-        <v>286985.3377344949</v>
+        <v>282820.806203864</v>
       </c>
       <c r="I8" t="n">
-        <v>-1229445.869668042</v>
+        <v>-1198111.928482303</v>
       </c>
       <c r="J8" t="n">
-        <v>-305186.4200093782</v>
+        <v>-309064.4812833543</v>
       </c>
       <c r="K8" t="n">
-        <v>-69322.8282606218</v>
+        <v>-70462.81403161223</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44549067.81327646</v>
+        <v>43485110.55453386</v>
       </c>
       <c r="C9" t="n">
-        <v>-171644950.7877054</v>
+        <v>-170146067.9621255</v>
       </c>
       <c r="D9" t="n">
-        <v>29583431.2794694</v>
+        <v>28675190.49999867</v>
       </c>
       <c r="E9" t="n">
-        <v>-1294412.205567126</v>
+        <v>-1470976.294074424</v>
       </c>
       <c r="F9" t="n">
-        <v>-17307477.90959779</v>
+        <v>-16869633.1802332</v>
       </c>
       <c r="G9" t="n">
-        <v>-4086739.665400695</v>
+        <v>-3965440.212841945</v>
       </c>
       <c r="H9" t="n">
-        <v>-1229445.869668042</v>
+        <v>-1198111.928482303</v>
       </c>
       <c r="I9" t="n">
-        <v>13732238.43392329</v>
+        <v>13379870.8193807</v>
       </c>
       <c r="J9" t="n">
-        <v>-1087846.08175756</v>
+        <v>-1006795.537455944</v>
       </c>
       <c r="K9" t="n">
-        <v>-345324.3819125487</v>
+        <v>-323174.7761271112</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2340521.296071955</v>
+        <v>2538006.34661707</v>
       </c>
       <c r="C10" t="n">
-        <v>-9264715.732167479</v>
+        <v>-9319113.296975804</v>
       </c>
       <c r="D10" t="n">
-        <v>3655445.366674128</v>
+        <v>3826962.990752989</v>
       </c>
       <c r="E10" t="n">
-        <v>-142884.5957050024</v>
+        <v>-101440.3649065482</v>
       </c>
       <c r="F10" t="n">
-        <v>1355248.186992848</v>
+        <v>1254380.192172263</v>
       </c>
       <c r="G10" t="n">
-        <v>532405.5943472488</v>
+        <v>502416.114790782</v>
       </c>
       <c r="H10" t="n">
-        <v>-305186.4200093782</v>
+        <v>-309064.4812833543</v>
       </c>
       <c r="I10" t="n">
-        <v>-1087846.08175756</v>
+        <v>-1006795.537455944</v>
       </c>
       <c r="J10" t="n">
-        <v>1102818.894434777</v>
+        <v>1074704.658998976</v>
       </c>
       <c r="K10" t="n">
-        <v>280917.6582588389</v>
+        <v>273462.4971443003</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>338416.3572458662</v>
+        <v>393523.3372458589</v>
       </c>
       <c r="C11" t="n">
-        <v>-1364850.914013479</v>
+        <v>-1386726.105998226</v>
       </c>
       <c r="D11" t="n">
-        <v>748678.0524112384</v>
+        <v>796448.5669007425</v>
       </c>
       <c r="E11" t="n">
-        <v>-28538.92300987191</v>
+        <v>-17230.28742155878</v>
       </c>
       <c r="F11" t="n">
-        <v>433025.4856837429</v>
+        <v>405463.7557837246</v>
       </c>
       <c r="G11" t="n">
-        <v>155215.9934330436</v>
+        <v>147070.6367823817</v>
       </c>
       <c r="H11" t="n">
-        <v>-69322.8282606218</v>
+        <v>-70462.81403161223</v>
       </c>
       <c r="I11" t="n">
-        <v>-345324.3819125487</v>
+        <v>-323174.7761271112</v>
       </c>
       <c r="J11" t="n">
-        <v>280917.6582588389</v>
+        <v>273462.4971443003</v>
       </c>
       <c r="K11" t="n">
-        <v>71933.39440612777</v>
+        <v>69952.84085905187</v>
       </c>
     </row>
   </sheetData>

--- a/dynamical_DE_nonfid/cmb/all.xlsx
+++ b/dynamical_DE_nonfid/cmb/all.xlsx
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>179726318.7752797</v>
+        <v>209051531.4652984</v>
       </c>
       <c r="C2" t="n">
-        <v>-684279674.308524</v>
+        <v>-735587809.3110509</v>
       </c>
       <c r="D2" t="n">
-        <v>133164111.0842395</v>
+        <v>161555701.5332739</v>
       </c>
       <c r="E2" t="n">
-        <v>-5301485.871778147</v>
+        <v>-4852490.824165525</v>
       </c>
       <c r="F2" t="n">
-        <v>-56142956.60137209</v>
+        <v>-66473229.52235723</v>
       </c>
       <c r="G2" t="n">
-        <v>-11998943.14466756</v>
+        <v>-14461748.75410303</v>
       </c>
       <c r="H2" t="n">
-        <v>-6436718.703385314</v>
+        <v>-7463213.873897064</v>
       </c>
       <c r="I2" t="n">
-        <v>43485110.55453386</v>
+        <v>51707841.00474619</v>
       </c>
       <c r="J2" t="n">
-        <v>2538006.34661707</v>
+        <v>2054003.471435804</v>
       </c>
       <c r="K2" t="n">
-        <v>393523.3372458589</v>
+        <v>227367.749666453</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-684279674.3085241</v>
+        <v>-735587809.3110509</v>
       </c>
       <c r="C3" t="n">
-        <v>3010811373.398757</v>
+        <v>2976209959.830989</v>
       </c>
       <c r="D3" t="n">
-        <v>-453274471.6905276</v>
+        <v>-522086791.9779352</v>
       </c>
       <c r="E3" t="n">
-        <v>33068744.31396467</v>
+        <v>31558011.55048786</v>
       </c>
       <c r="F3" t="n">
-        <v>221180647.2978463</v>
+        <v>238636749.7606161</v>
       </c>
       <c r="G3" t="n">
-        <v>46782212.50549188</v>
+        <v>50856554.93252619</v>
       </c>
       <c r="H3" t="n">
-        <v>23017830.30519351</v>
+        <v>25110289.18276101</v>
       </c>
       <c r="I3" t="n">
-        <v>-170146067.9621255</v>
+        <v>-184145288.7259212</v>
       </c>
       <c r="J3" t="n">
-        <v>-9319113.296975804</v>
+        <v>-8875518.577786302</v>
       </c>
       <c r="K3" t="n">
-        <v>-1386726.105998227</v>
+        <v>-1198112.802082309</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133164111.0842395</v>
+        <v>161555701.5332739</v>
       </c>
       <c r="C4" t="n">
-        <v>-453274471.6905276</v>
+        <v>-522086791.9779352</v>
       </c>
       <c r="D4" t="n">
-        <v>109374543.1721104</v>
+        <v>134632948.2700467</v>
       </c>
       <c r="E4" t="n">
-        <v>-2368001.637530286</v>
+        <v>-2200936.284889752</v>
       </c>
       <c r="F4" t="n">
-        <v>-37002889.86396396</v>
+        <v>-46487920.65828581</v>
       </c>
       <c r="G4" t="n">
-        <v>-7528183.426049238</v>
+        <v>-9733572.73610968</v>
       </c>
       <c r="H4" t="n">
-        <v>-5358456.88315504</v>
+        <v>-6367158.434989806</v>
       </c>
       <c r="I4" t="n">
-        <v>28675190.49999867</v>
+        <v>36202454.05514385</v>
       </c>
       <c r="J4" t="n">
-        <v>3826962.990752989</v>
+        <v>3644955.770628864</v>
       </c>
       <c r="K4" t="n">
-        <v>796448.5669007425</v>
+        <v>709448.9370135852</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5301485.871778147</v>
+        <v>-4852490.824165525</v>
       </c>
       <c r="C5" t="n">
-        <v>33068744.31396466</v>
+        <v>31558011.55048787</v>
       </c>
       <c r="D5" t="n">
-        <v>-2368001.637530287</v>
+        <v>-2200936.284889752</v>
       </c>
       <c r="E5" t="n">
-        <v>936731.4425528144</v>
+        <v>1114651.801915904</v>
       </c>
       <c r="F5" t="n">
-        <v>1900676.716547794</v>
+        <v>1735297.880047496</v>
       </c>
       <c r="G5" t="n">
-        <v>379534.2690776868</v>
+        <v>322720.774998914</v>
       </c>
       <c r="H5" t="n">
-        <v>129968.5455609026</v>
+        <v>116080.9528587897</v>
       </c>
       <c r="I5" t="n">
-        <v>-1470976.294074424</v>
+        <v>-1322969.289314048</v>
       </c>
       <c r="J5" t="n">
-        <v>-101440.3649065482</v>
+        <v>-154911.8577843752</v>
       </c>
       <c r="K5" t="n">
-        <v>-17230.28742155878</v>
+        <v>-31371.96676259759</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-56142956.60137209</v>
+        <v>-66473229.52235723</v>
       </c>
       <c r="C6" t="n">
-        <v>221180647.2978463</v>
+        <v>238636749.7606161</v>
       </c>
       <c r="D6" t="n">
-        <v>-37002889.86396396</v>
+        <v>-46487920.65828581</v>
       </c>
       <c r="E6" t="n">
-        <v>1900676.716547794</v>
+        <v>1735297.880047496</v>
       </c>
       <c r="F6" t="n">
-        <v>21822591.95535067</v>
+        <v>26141803.65416903</v>
       </c>
       <c r="G6" t="n">
-        <v>5099104.950243197</v>
+        <v>6187152.832831174</v>
       </c>
       <c r="H6" t="n">
-        <v>1551995.646661993</v>
+        <v>1847551.648398456</v>
       </c>
       <c r="I6" t="n">
-        <v>-16869633.1802332</v>
+        <v>-20307765.06701478</v>
       </c>
       <c r="J6" t="n">
-        <v>1254380.192172263</v>
+        <v>1761387.932595035</v>
       </c>
       <c r="K6" t="n">
-        <v>405463.7557837246</v>
+        <v>550843.7974945904</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-11998943.14466756</v>
+        <v>-14461748.75410303</v>
       </c>
       <c r="C7" t="n">
-        <v>46782212.50549188</v>
+        <v>50856554.93252616</v>
       </c>
       <c r="D7" t="n">
-        <v>-7528183.426049238</v>
+        <v>-9733572.73610968</v>
       </c>
       <c r="E7" t="n">
-        <v>379534.2690776868</v>
+        <v>322720.774998914</v>
       </c>
       <c r="F7" t="n">
-        <v>5099104.950243197</v>
+        <v>6187152.832831174</v>
       </c>
       <c r="G7" t="n">
-        <v>1239055.078393945</v>
+        <v>1519000.29400283</v>
       </c>
       <c r="H7" t="n">
-        <v>284765.0145282443</v>
+        <v>349781.5542092127</v>
       </c>
       <c r="I7" t="n">
-        <v>-3965440.212841945</v>
+        <v>-4832062.974640697</v>
       </c>
       <c r="J7" t="n">
-        <v>502416.114790782</v>
+        <v>656651.2304007352</v>
       </c>
       <c r="K7" t="n">
-        <v>147070.6367823817</v>
+        <v>190299.5852746114</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-6436718.703385314</v>
+        <v>-7463213.873897064</v>
       </c>
       <c r="C8" t="n">
-        <v>23017830.30519351</v>
+        <v>25110289.18276101</v>
       </c>
       <c r="D8" t="n">
-        <v>-5358456.88315504</v>
+        <v>-6367158.434989806</v>
       </c>
       <c r="E8" t="n">
-        <v>129968.5455609026</v>
+        <v>116080.9528587896</v>
       </c>
       <c r="F8" t="n">
-        <v>1551995.646661993</v>
+        <v>1847551.648398456</v>
       </c>
       <c r="G8" t="n">
-        <v>284765.0145282443</v>
+        <v>349781.5542092127</v>
       </c>
       <c r="H8" t="n">
-        <v>282820.806203864</v>
+        <v>324683.0014483123</v>
       </c>
       <c r="I8" t="n">
-        <v>-1198111.928482303</v>
+        <v>-1434322.472016788</v>
       </c>
       <c r="J8" t="n">
-        <v>-309064.4812833543</v>
+        <v>-324581.9129763995</v>
       </c>
       <c r="K8" t="n">
-        <v>-70462.81403161223</v>
+        <v>-73020.09566896482</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43485110.55453386</v>
+        <v>51707841.00474619</v>
       </c>
       <c r="C9" t="n">
-        <v>-170146067.9621255</v>
+        <v>-184145288.7259211</v>
       </c>
       <c r="D9" t="n">
-        <v>28675190.49999867</v>
+        <v>36202454.05514385</v>
       </c>
       <c r="E9" t="n">
-        <v>-1470976.294074424</v>
+        <v>-1322969.289314048</v>
       </c>
       <c r="F9" t="n">
-        <v>-16869633.1802332</v>
+        <v>-20307765.06701478</v>
       </c>
       <c r="G9" t="n">
-        <v>-3965440.212841945</v>
+        <v>-4832062.974640697</v>
       </c>
       <c r="H9" t="n">
-        <v>-1198111.928482303</v>
+        <v>-1434322.472016788</v>
       </c>
       <c r="I9" t="n">
-        <v>13379870.8193807</v>
+        <v>16114781.21753684</v>
       </c>
       <c r="J9" t="n">
-        <v>-1006795.537455944</v>
+        <v>-1412284.200501196</v>
       </c>
       <c r="K9" t="n">
-        <v>-323174.7761271112</v>
+        <v>-439352.9354162303</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2538006.34661707</v>
+        <v>2054003.471435803</v>
       </c>
       <c r="C10" t="n">
-        <v>-9319113.296975804</v>
+        <v>-8875518.577786304</v>
       </c>
       <c r="D10" t="n">
-        <v>3826962.990752989</v>
+        <v>3644955.770628864</v>
       </c>
       <c r="E10" t="n">
-        <v>-101440.3649065482</v>
+        <v>-154911.8577843752</v>
       </c>
       <c r="F10" t="n">
-        <v>1254380.192172263</v>
+        <v>1761387.932595035</v>
       </c>
       <c r="G10" t="n">
-        <v>502416.114790782</v>
+        <v>656651.2304007352</v>
       </c>
       <c r="H10" t="n">
-        <v>-309064.4812833543</v>
+        <v>-324581.9129763995</v>
       </c>
       <c r="I10" t="n">
-        <v>-1006795.537455944</v>
+        <v>-1412284.200501196</v>
       </c>
       <c r="J10" t="n">
-        <v>1074704.658998976</v>
+        <v>1261487.815355783</v>
       </c>
       <c r="K10" t="n">
-        <v>273462.4971443003</v>
+        <v>322243.5240145934</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>393523.3372458589</v>
+        <v>227367.749666453</v>
       </c>
       <c r="C11" t="n">
-        <v>-1386726.105998226</v>
+        <v>-1198112.802082309</v>
       </c>
       <c r="D11" t="n">
-        <v>796448.5669007425</v>
+        <v>709448.9370135854</v>
       </c>
       <c r="E11" t="n">
-        <v>-17230.28742155878</v>
+        <v>-31371.96676259758</v>
       </c>
       <c r="F11" t="n">
-        <v>405463.7557837246</v>
+        <v>550843.7974945904</v>
       </c>
       <c r="G11" t="n">
-        <v>147070.6367823817</v>
+        <v>190299.5852746114</v>
       </c>
       <c r="H11" t="n">
-        <v>-70462.81403161223</v>
+        <v>-73020.09566896482</v>
       </c>
       <c r="I11" t="n">
-        <v>-323174.7761271112</v>
+        <v>-439352.9354162305</v>
       </c>
       <c r="J11" t="n">
-        <v>273462.4971443003</v>
+        <v>322243.5240145932</v>
       </c>
       <c r="K11" t="n">
-        <v>69952.84085905187</v>
+        <v>82749.64491436683</v>
       </c>
     </row>
   </sheetData>
